--- a/РАБОЧИЙ СТОЛ/!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!Доп Заказ 08.10 (от Титенок КИ - разово; ЗПФ на постоянку).xlsx
+++ b/РАБОЧИЙ СТОЛ/!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!Доп Заказ 08.10 (от Титенок КИ - разово; ЗПФ на постоянку).xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ЭтаКнига"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8BE9A5-13EE-4407-85BC-845BAD34F7B2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFA2862-7E2E-41E8-BDD0-5D789600FDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,16 +16,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новое время'!$A$7:$AB$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Новое время'!$A$1:$G$27</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1" fullPrecision="0"/>
+  <calcPr calcId="191029" refMode="R1C1" fullPrecision="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1727,6 +1721,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="27" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1749,12 +1761,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="34" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1781,18 +1787,6 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3411,26 +3405,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4301,36 +4275,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4641,6 +4585,146 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4751,6 +4835,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4821,46 +4915,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4941,46 +4995,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -5310,6 +5324,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -5480,16 +5518,82 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5530,116 +5634,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6028,9 +6022,9 @@
       <c r="C2" s="120"/>
       <c r="D2" s="120"/>
       <c r="E2" s="23"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
       <c r="I2" s="98"/>
       <c r="J2" s="98"/>
       <c r="L2" s="82"/>
@@ -6081,77 +6075,77 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="152" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="150" t="s">
+      <c r="B5" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="152" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="152" t="s">
+      <c r="C5" s="156" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="152" t="s">
+      <c r="E5" s="156" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="154" t="s">
+      <c r="F5" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="144" t="s">
+      <c r="G5" s="150" t="s">
         <v>232</v>
       </c>
-      <c r="H5" s="144" t="s">
+      <c r="H5" s="150" t="s">
         <v>233</v>
       </c>
-      <c r="I5" s="144" t="s">
+      <c r="I5" s="150" t="s">
         <v>234</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="150" t="s">
         <v>235</v>
       </c>
       <c r="K5" s="96"/>
-      <c r="L5" s="146" t="s">
+      <c r="L5" s="142" t="s">
         <v>220</v>
       </c>
-      <c r="M5" s="156" t="s">
+      <c r="M5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="N5" s="158" t="s">
+      <c r="N5" s="140" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="146" t="s">
+      <c r="P5" s="142" t="s">
         <v>218</v>
       </c>
-      <c r="Q5" s="156" t="s">
+      <c r="Q5" s="138" t="s">
         <v>219</v>
       </c>
-      <c r="R5" s="158" t="s">
+      <c r="R5" s="140" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="139.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="149"/>
-      <c r="B6" s="151"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="155"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="145"/>
-      <c r="I6" s="145"/>
-      <c r="J6" s="145"/>
+      <c r="A6" s="153"/>
+      <c r="B6" s="155"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="151"/>
+      <c r="H6" s="151"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="151"/>
       <c r="K6" s="94"/>
-      <c r="L6" s="147"/>
-      <c r="M6" s="157"/>
-      <c r="N6" s="159"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="139"/>
+      <c r="N6" s="141"/>
       <c r="O6" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="P6" s="147"/>
-      <c r="Q6" s="157"/>
-      <c r="R6" s="159"/>
+      <c r="P6" s="143"/>
+      <c r="Q6" s="139"/>
+      <c r="R6" s="141"/>
     </row>
     <row r="7" spans="1:22" customFormat="1" ht="42.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56"/>
@@ -6331,14 +6325,14 @@
       <c r="V10" s="99"/>
     </row>
     <row r="11" spans="1:22" s="27" customFormat="1" ht="32.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="138" t="s">
+      <c r="A11" s="144" t="s">
         <v>238</v>
       </c>
-      <c r="B11" s="139"/>
-      <c r="C11" s="139"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="140"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="146"/>
       <c r="G11" s="128">
         <f>G8+G9+G10</f>
         <v>150</v>
@@ -6706,14 +6700,14 @@
       <c r="V19" s="99"/>
     </row>
     <row r="20" spans="1:22" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="141" t="s">
+      <c r="A20" s="147" t="s">
         <v>238</v>
       </c>
-      <c r="B20" s="142"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="142"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="142"/>
+      <c r="B20" s="148"/>
+      <c r="C20" s="148"/>
+      <c r="D20" s="148"/>
+      <c r="E20" s="148"/>
+      <c r="F20" s="148"/>
       <c r="G20" s="137">
         <f>G13+G14+G15+G16+G17+G18</f>
         <v>320</v>
@@ -6829,11 +6823,6 @@
     <sortCondition ref="C9"/>
   </sortState>
   <mergeCells count="19">
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="R5:R6"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="F2:H2"/>
@@ -6848,71 +6837,76 @@
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="G5:G6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
   </mergeCells>
+  <conditionalFormatting sqref="A1:A4">
+    <cfRule type="duplicateValues" dxfId="388" priority="13340"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="388" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="1018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A7">
-    <cfRule type="duplicateValues" dxfId="387" priority="1015"/>
     <cfRule type="duplicateValues" dxfId="386" priority="1016"/>
     <cfRule type="duplicateValues" dxfId="385" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="1015"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="duplicateValues" dxfId="383" priority="13351"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="13346"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="13345"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="13344"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="13343"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="13342"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="13341"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="13347"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="13348"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="13349"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="13350"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="duplicateValues" dxfId="372" priority="13339"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="13338"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="13337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:A17">
-    <cfRule type="duplicateValues" dxfId="384" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="383" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="382" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="381" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="380" priority="13325"/>
-    <cfRule type="duplicateValues" dxfId="379" priority="13326"/>
-    <cfRule type="duplicateValues" dxfId="378" priority="13327"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="13325"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="13326"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="13327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="377" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="376" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="375" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="374" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="373" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A27">
-    <cfRule type="duplicateValues" dxfId="372" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A1048576 A1:A7">
-    <cfRule type="duplicateValues" dxfId="371" priority="775"/>
-    <cfRule type="duplicateValues" dxfId="370" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:A1048576 A1:A4">
-    <cfRule type="duplicateValues" dxfId="369" priority="8865"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="8865"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I19 I12">
-    <cfRule type="cellIs" dxfId="368" priority="11" operator="greaterThan">
+  <conditionalFormatting sqref="I12 I19">
+    <cfRule type="cellIs" dxfId="353" priority="12" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="352" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="366" priority="13337"/>
-    <cfRule type="duplicateValues" dxfId="365" priority="13338"/>
-    <cfRule type="duplicateValues" dxfId="364" priority="13339"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4">
-    <cfRule type="duplicateValues" dxfId="363" priority="13340"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="362" priority="13341"/>
-    <cfRule type="duplicateValues" dxfId="361" priority="13342"/>
-    <cfRule type="duplicateValues" dxfId="360" priority="13343"/>
-    <cfRule type="duplicateValues" dxfId="359" priority="13344"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="13345"/>
-    <cfRule type="duplicateValues" dxfId="357" priority="13346"/>
-    <cfRule type="duplicateValues" dxfId="356" priority="13347"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="13348"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="13349"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="13350"/>
-    <cfRule type="duplicateValues" dxfId="352" priority="13351"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -6937,22 +6931,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:26" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="148" t="s">
+      <c r="A2" s="152" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="152" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="152" t="s">
+      <c r="C2" s="156" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="152" t="s">
+      <c r="E2" s="156" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="154" t="s">
+      <c r="F2" s="158" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="75">
@@ -7001,12 +6995,12 @@
       <c r="Z2" s="76"/>
     </row>
     <row r="3" spans="1:26" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="149"/>
-      <c r="B3" s="151"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
-      <c r="F3" s="155"/>
+      <c r="A3" s="153"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="159"/>
       <c r="G3" s="75" t="s">
         <v>200</v>
       </c>
@@ -17927,114 +17921,114 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A4">
     <cfRule type="duplicateValues" dxfId="350" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="349" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="348" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="347" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="346" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="268"/>
     <cfRule type="duplicateValues" dxfId="345" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="344" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="343" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="342" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="341" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="340" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="339" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="271"/>
     <cfRule type="duplicateValues" dxfId="338" priority="274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="337" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="336" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="334" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="333" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="332" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="330" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="87"/>
     <cfRule type="duplicateValues" dxfId="329" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
     <cfRule type="duplicateValues" dxfId="327" priority="298"/>
     <cfRule type="duplicateValues" dxfId="326" priority="299"/>
     <cfRule type="duplicateValues" dxfId="325" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="324" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="323" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="301"/>
     <cfRule type="duplicateValues" dxfId="322" priority="303"/>
     <cfRule type="duplicateValues" dxfId="321" priority="304"/>
     <cfRule type="duplicateValues" dxfId="320" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="308"/>
     <cfRule type="duplicateValues" dxfId="318" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A20">
     <cfRule type="duplicateValues" dxfId="316" priority="352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="315" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="278"/>
     <cfRule type="duplicateValues" dxfId="314" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="313" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="281"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="308" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="284"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A26">
-    <cfRule type="duplicateValues" dxfId="304" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="297"/>
     <cfRule type="duplicateValues" dxfId="303" priority="288"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="301" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="291"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="294"/>
     <cfRule type="duplicateValues" dxfId="298" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="duplicateValues" dxfId="293" priority="315"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="316"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="318"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="322"/>
     <cfRule type="duplicateValues" dxfId="288" priority="320"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="321"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="322"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="323"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="324"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" dxfId="282" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="281" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29">
-    <cfRule type="duplicateValues" dxfId="278" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="66"/>
     <cfRule type="duplicateValues" dxfId="277" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="64"/>
     <cfRule type="duplicateValues" dxfId="275" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30 A21 A23">
     <cfRule type="duplicateValues" dxfId="274" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:A32">
     <cfRule type="duplicateValues" dxfId="270" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
-    <cfRule type="duplicateValues" dxfId="269" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36">
     <cfRule type="duplicateValues" dxfId="265" priority="208"/>
@@ -18046,38 +18040,38 @@
     <cfRule type="duplicateValues" dxfId="263" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
-    <cfRule type="duplicateValues" dxfId="262" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="30"/>
     <cfRule type="duplicateValues" dxfId="260" priority="32"/>
     <cfRule type="duplicateValues" dxfId="259" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:A44">
-    <cfRule type="duplicateValues" dxfId="258" priority="309"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46">
-    <cfRule type="duplicateValues" dxfId="256" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="253" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A50 A52">
-    <cfRule type="duplicateValues" dxfId="252" priority="224"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="250" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="249" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="246" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="233"/>
     <cfRule type="duplicateValues" dxfId="244" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="242" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="12"/>
     <cfRule type="duplicateValues" dxfId="240" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53 A45">
     <cfRule type="duplicateValues" dxfId="238" priority="205"/>
@@ -18086,37 +18080,37 @@
     <cfRule type="duplicateValues" dxfId="237" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:A55 A2:A5 A125:A127 A31:A33 A69:A71 A82:A83 A102 A94:A97 A35:A39 A104:A110 A66 A60:A61 A88:A89 A129 A139:A155 A9:A20 A85:A86 A131:A134 A41:A45 A157:A162">
-    <cfRule type="duplicateValues" dxfId="236" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="234" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="232" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="225" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="223" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="117"/>
     <cfRule type="duplicateValues" dxfId="222" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" dxfId="221" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="217" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="216" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="214" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62">
     <cfRule type="duplicateValues" dxfId="213" priority="158"/>
@@ -18125,61 +18119,61 @@
     <cfRule type="duplicateValues" dxfId="210" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="209" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="155"/>
     <cfRule type="duplicateValues" dxfId="206" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="duplicateValues" dxfId="205" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
-    <cfRule type="duplicateValues" dxfId="201" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A68">
     <cfRule type="duplicateValues" dxfId="197" priority="140"/>
     <cfRule type="duplicateValues" dxfId="196" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:A70 A54:A55 A66 A60:A61">
     <cfRule type="duplicateValues" dxfId="188" priority="256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A71">
-    <cfRule type="duplicateValues" dxfId="187" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A74">
-    <cfRule type="duplicateValues" dxfId="185" priority="311"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A81">
-    <cfRule type="duplicateValues" dxfId="181" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="355"/>
     <cfRule type="duplicateValues" dxfId="180" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="353"/>
     <cfRule type="duplicateValues" dxfId="178" priority="356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83">
-    <cfRule type="duplicateValues" dxfId="177" priority="326"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
-    <cfRule type="duplicateValues" dxfId="175" priority="328"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="329"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85 A82">
     <cfRule type="duplicateValues" dxfId="172" priority="203"/>
@@ -18188,37 +18182,37 @@
     <cfRule type="duplicateValues" dxfId="171" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A86">
-    <cfRule type="duplicateValues" dxfId="170" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A89">
     <cfRule type="duplicateValues" dxfId="167" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A90:A91 A87">
-    <cfRule type="duplicateValues" dxfId="166" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A92">
-    <cfRule type="duplicateValues" dxfId="162" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="104"/>
     <cfRule type="duplicateValues" dxfId="155" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93">
-    <cfRule type="duplicateValues" dxfId="152" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="332"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="332"/>
     <cfRule type="duplicateValues" dxfId="149" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A94">
     <cfRule type="duplicateValues" dxfId="147" priority="200"/>
@@ -18239,8 +18233,8 @@
     <cfRule type="duplicateValues" dxfId="140" priority="341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
-    <cfRule type="duplicateValues" dxfId="139" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103 A98:A100">
     <cfRule type="duplicateValues" dxfId="137" priority="251"/>
@@ -18254,10 +18248,10 @@
     <cfRule type="duplicateValues" dxfId="133" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111:A115">
-    <cfRule type="duplicateValues" dxfId="132" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
     <cfRule type="duplicateValues" dxfId="128" priority="259"/>
@@ -18267,38 +18261,38 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A117 A119:A121">
     <cfRule type="duplicateValues" dxfId="124" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="345"/>
     <cfRule type="duplicateValues" dxfId="122" priority="344"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="120" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122:A124">
-    <cfRule type="duplicateValues" dxfId="116" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="74"/>
     <cfRule type="duplicateValues" dxfId="115" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A125">
-    <cfRule type="duplicateValues" dxfId="113" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:A127">
     <cfRule type="duplicateValues" dxfId="111" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A128">
     <cfRule type="duplicateValues" dxfId="110" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A129">
     <cfRule type="duplicateValues" dxfId="101" priority="187"/>
@@ -18306,14 +18300,14 @@
     <cfRule type="duplicateValues" dxfId="99" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A130">
-    <cfRule type="duplicateValues" dxfId="98" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="264"/>
     <cfRule type="duplicateValues" dxfId="97" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A131">
-    <cfRule type="duplicateValues" dxfId="95" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A133">
     <cfRule type="duplicateValues" dxfId="92" priority="194"/>
@@ -18323,22 +18317,22 @@
     <cfRule type="duplicateValues" dxfId="90" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135">
-    <cfRule type="duplicateValues" dxfId="89" priority="346"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="346"/>
     <cfRule type="duplicateValues" dxfId="87" priority="348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A136:A138">
     <cfRule type="duplicateValues" dxfId="86" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="29"/>
     <cfRule type="duplicateValues" dxfId="84" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A139:A141 A134">
     <cfRule type="duplicateValues" dxfId="82" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A142">
-    <cfRule type="duplicateValues" dxfId="81" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A143:A144">
     <cfRule type="duplicateValues" dxfId="79" priority="181"/>
@@ -18377,8 +18371,8 @@
   <conditionalFormatting sqref="A165">
     <cfRule type="duplicateValues" dxfId="65" priority="68"/>
     <cfRule type="duplicateValues" dxfId="64" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A166">
     <cfRule type="duplicateValues" dxfId="61" priority="349"/>
@@ -18387,20 +18381,20 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A167">
     <cfRule type="duplicateValues" dxfId="58" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="14"/>
     <cfRule type="duplicateValues" dxfId="55" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A168">
-    <cfRule type="duplicateValues" dxfId="54" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="19"/>
     <cfRule type="duplicateValues" dxfId="53" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A169 A178:A179 A181">
-    <cfRule type="duplicateValues" dxfId="50" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="124"/>
     <cfRule type="duplicateValues" dxfId="49" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A169">
     <cfRule type="duplicateValues" dxfId="47" priority="122"/>
@@ -18409,26 +18403,26 @@
   <conditionalFormatting sqref="A170:A173">
     <cfRule type="duplicateValues" dxfId="45" priority="60"/>
     <cfRule type="duplicateValues" dxfId="44" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A174">
-    <cfRule type="duplicateValues" dxfId="41" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A175">
-    <cfRule type="duplicateValues" dxfId="37" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A176">
     <cfRule type="duplicateValues" dxfId="33" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A177">
     <cfRule type="duplicateValues" dxfId="29" priority="44"/>
@@ -18440,11 +18434,11 @@
     <cfRule type="duplicateValues" dxfId="25" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A180">
-    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
     <cfRule type="duplicateValues" dxfId="22" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A182">
     <cfRule type="duplicateValues" dxfId="19" priority="39"/>
@@ -18454,16 +18448,16 @@
     <cfRule type="duplicateValues" dxfId="15" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A183">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
     <cfRule type="duplicateValues" dxfId="12" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A184">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:B6">
     <cfRule type="duplicateValues" dxfId="6" priority="275"/>
